--- a/data/processed/harmonization/Carbon__Water-extractable_organic_carbon/harmonized.xlsx
+++ b/data/processed/harmonization/Carbon__Water-extractable_organic_carbon/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -14054,12 +14054,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr"/>
@@ -14102,12 +14102,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
@@ -14150,12 +14150,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3:3</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
@@ -14198,12 +14198,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
@@ -14246,12 +14246,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr"/>
@@ -14294,12 +14294,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr"/>
@@ -14342,12 +14342,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2:7</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr"/>
@@ -14390,12 +14390,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3:8</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr"/>
@@ -14438,12 +14438,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr"/>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5:10</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr"/>
@@ -14534,12 +14534,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
@@ -14582,12 +14582,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr"/>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr"/>
@@ -14678,12 +14678,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr"/>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr"/>
@@ -14774,12 +14774,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0209</t>
+          <t>upland:10.58052/IEEXG0209</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr"/>
@@ -14822,12 +14822,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020N</t>
+          <t>transition:10.58052/IEEXG020N</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
@@ -14870,12 +14870,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0211</t>
+          <t>wetland:10.58052/IEEXG0211</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr"/>
@@ -14918,12 +14918,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021F</t>
+          <t>upland:10.58052/IEEXG021F</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr"/>
@@ -14966,12 +14966,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021T</t>
+          <t>transition:10.58052/IEEXG021T</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr"/>
@@ -15014,12 +15014,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0227</t>
+          <t>wetland:10.58052/IEEXG0227</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr"/>
@@ -15062,12 +15062,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022L</t>
+          <t>upland:10.58052/IEEXG022L</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr"/>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022Z</t>
+          <t>transition:10.58052/IEEXG022Z</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr"/>
@@ -15158,12 +15158,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023D</t>
+          <t>wetland:10.58052/IEEXG023D</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr"/>
@@ -15206,12 +15206,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023R</t>
+          <t>upland:10.58052/IEEXG023R</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr"/>
@@ -15254,12 +15254,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0245</t>
+          <t>transition:10.58052/IEEXG0245</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr"/>
@@ -15302,12 +15302,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024J</t>
+          <t>wetland:10.58052/IEEXG024J</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr"/>
@@ -15350,12 +15350,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024X</t>
+          <t>upland:10.58052/IEEXG024X</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr"/>
@@ -15398,12 +15398,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025B</t>
+          <t>transition:10.58052/IEEXG025B</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr"/>
@@ -15446,12 +15446,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025P</t>
+          <t>wetland:10.58052/IEEXG025P</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr"/>
@@ -15494,12 +15494,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0263</t>
+          <t>upland:10.58052/IEEXG0263</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr"/>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026H</t>
+          <t>transition:10.58052/IEEXG026H</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr"/>
@@ -15590,12 +15590,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026V</t>
+          <t>wetland:10.58052/IEEXG026V</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr"/>
@@ -15638,12 +15638,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0279</t>
+          <t>upland:10.58052/IEEXG0279</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr"/>
@@ -15686,12 +15686,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027N</t>
+          <t>transition:10.58052/IEEXG027N</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr"/>
@@ -15734,12 +15734,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0281</t>
+          <t>wetland:10.58052/IEEXG0281</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr"/>
@@ -15782,12 +15782,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028F</t>
+          <t>upland:10.58052/IEEXG028F</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr"/>
@@ -15830,12 +15830,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028T</t>
+          <t>transition:10.58052/IEEXG028T</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr"/>
@@ -15878,12 +15878,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0297</t>
+          <t>wetland:10.58052/IEEXG0297</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr"/>
@@ -15926,12 +15926,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029L</t>
+          <t>upland:10.58052/IEEXG029L</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr"/>
@@ -15974,12 +15974,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029Z</t>
+          <t>transition:10.58052/IEEXG029Z</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr"/>
@@ -16022,12 +16022,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AD</t>
+          <t>wetland:10.58052/IEEXG02AD</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr"/>
@@ -16070,12 +16070,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AR</t>
+          <t>upland:10.58052/IEEXG02AR</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
@@ -16118,12 +16118,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B5</t>
+          <t>transition:10.58052/IEEXG02B5</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr"/>
@@ -16166,12 +16166,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BJ</t>
+          <t>wetland:10.58052/IEEXG02BJ</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr"/>
@@ -16214,12 +16214,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BX</t>
+          <t>upland:10.58052/IEEXG02BX</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr"/>
@@ -16262,12 +16262,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CB</t>
+          <t>transition:10.58052/IEEXG02CB</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr"/>
@@ -16310,12 +16310,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CP</t>
+          <t>wetland:10.58052/IEEXG02CP</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr"/>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D3</t>
+          <t>upland:10.58052/IEEXG02D3</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr"/>
@@ -16406,12 +16406,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DH</t>
+          <t>transition:10.58052/IEEXG02DH</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr"/>
@@ -16454,12 +16454,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DV</t>
+          <t>wetland:10.58052/IEEXG02DV</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr"/>
@@ -16502,12 +16502,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02E9</t>
+          <t>upland:10.58052/IEEXG02E9</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr"/>
@@ -16550,12 +16550,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EN</t>
+          <t>transition:10.58052/IEEXG02EN</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr"/>
@@ -16598,12 +16598,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F1</t>
+          <t>wetland:10.58052/IEEXG02F1</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr"/>
@@ -16646,12 +16646,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FF</t>
+          <t>upland:10.58052/IEEXG02FF</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr"/>
@@ -16694,12 +16694,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FT</t>
+          <t>transition:10.58052/IEEXG02FT</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr"/>
@@ -16742,12 +16742,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G7</t>
+          <t>wetland:10.58052/IEEXG02G7</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr"/>
@@ -16790,12 +16790,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GL</t>
+          <t>upland:10.58052/IEEXG02GL</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr"/>
@@ -16838,12 +16838,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GZ</t>
+          <t>transition:10.58052/IEEXG02GZ</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr"/>
@@ -16886,12 +16886,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HD</t>
+          <t>wetland:10.58052/IEEXG02HD</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr"/>
@@ -16934,12 +16934,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HR</t>
+          <t>upland:10.58052/IEEXG02HR</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr"/>
@@ -16982,12 +16982,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I5</t>
+          <t>transition:10.58052/IEEXG02I5</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr"/>
@@ -17030,12 +17030,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IJ</t>
+          <t>wetland:10.58052/IEEXG02IJ</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr"/>
@@ -17078,12 +17078,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IX</t>
+          <t>upland:10.58052/IEEXG02IX</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr"/>
@@ -17126,12 +17126,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JB</t>
+          <t>transition:10.58052/IEEXG02JB</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JP</t>
+          <t>wetland:10.58052/IEEXG02JP</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr"/>
@@ -17222,12 +17222,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K3</t>
+          <t>upland:10.58052/IEEXG02K3</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
@@ -17270,12 +17270,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KH</t>
+          <t>transition:10.58052/IEEXG02KH</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr"/>
@@ -17318,12 +17318,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KV</t>
+          <t>wetland:10.58052/IEEXG02KV</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr"/>
@@ -17366,12 +17366,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02L9</t>
+          <t>upland:10.58052/IEEXG02L9</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr"/>
@@ -17414,12 +17414,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LN</t>
+          <t>transition:10.58052/IEEXG02LN</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr"/>
@@ -17462,12 +17462,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M1</t>
+          <t>wetland:10.58052/IEEXG02M1</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr"/>
@@ -17510,12 +17510,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MF</t>
+          <t>upland:10.58052/IEEXG02MF</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
@@ -17558,12 +17558,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MT</t>
+          <t>transition:10.58052/IEEXG02MT</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr"/>
@@ -17606,12 +17606,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N7</t>
+          <t>wetland:10.58052/IEEXG02N7</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
@@ -17654,12 +17654,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NL</t>
+          <t>upland:10.58052/IEEXG02NL</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr"/>
@@ -17702,12 +17702,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NZ</t>
+          <t>transition:10.58052/IEEXG02NZ</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
@@ -17750,12 +17750,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OD</t>
+          <t>wetland:10.58052/IEEXG02OD</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr"/>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OR</t>
+          <t>upland:10.58052/IEEXG02OR</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
@@ -17846,12 +17846,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P5</t>
+          <t>transition:10.58052/IEEXG02P5</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr"/>
@@ -17894,12 +17894,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PJ</t>
+          <t>wetland:10.58052/IEEXG02PJ</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
@@ -17942,12 +17942,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PX</t>
+          <t>upland:10.58052/IEEXG02PX</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
@@ -17990,12 +17990,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QB</t>
+          <t>transition:10.58052/IEEXG02QB</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
@@ -18038,12 +18038,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QP</t>
+          <t>wetland:10.58052/IEEXG02QP</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr"/>
@@ -18086,12 +18086,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02S9</t>
+          <t>upland:10.58052/IEEXG02S9</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr"/>
@@ -18134,12 +18134,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SN</t>
+          <t>transition:10.58052/IEEXG02SN</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr"/>
@@ -18182,12 +18182,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T1</t>
+          <t>wetland:10.58052/IEEXG02T1</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TF</t>
+          <t>upland:10.58052/IEEXG02TF</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr"/>
@@ -18278,12 +18278,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TT</t>
+          <t>transition:10.58052/IEEXG02TT</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr"/>
@@ -18326,12 +18326,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U7</t>
+          <t>wetland:10.58052/IEEXG02U7</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr"/>
@@ -18374,12 +18374,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UL</t>
+          <t>upland:10.58052/IEEXG02UL</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -18422,12 +18422,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UZ</t>
+          <t>transition:10.58052/IEEXG02UZ</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr"/>
@@ -18470,12 +18470,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VD</t>
+          <t>wetland:10.58052/IEEXG02VD</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VR</t>
+          <t>upland:10.58052/IEEXG02VR</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
@@ -18566,12 +18566,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W5</t>
+          <t>transition:10.58052/IEEXG02W5</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -18614,12 +18614,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WJ</t>
+          <t>wetland:10.58052/IEEXG02WJ</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr"/>
@@ -18662,12 +18662,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WX</t>
+          <t>upland:10.58052/IEEXG02WX</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
@@ -18710,12 +18710,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XB</t>
+          <t>transition:10.58052/IEEXG02XB</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr"/>
@@ -18758,12 +18758,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XP</t>
+          <t>wetland:10.58052/IEEXG02XP</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
@@ -18806,12 +18806,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y3</t>
+          <t>upland:10.58052/IEEXG02Y3</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
@@ -18854,12 +18854,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YH</t>
+          <t>transition:10.58052/IEEXG02YH</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
@@ -18902,12 +18902,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YV</t>
+          <t>wetland:10.58052/IEEXG02YV</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr"/>
@@ -18950,12 +18950,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Z9</t>
+          <t>upland:10.58052/IEEXG02Z9</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
@@ -18998,12 +18998,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZN</t>
+          <t>transition:10.58052/IEEXG02ZN</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -19046,12 +19046,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0301</t>
+          <t>wetland:10.58052/IEEXG0301</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -19094,12 +19094,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030F</t>
+          <t>upland:10.58052/IEEXG030F</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -19142,12 +19142,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030T</t>
+          <t>transition:10.58052/IEEXG030T</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0317</t>
+          <t>wetland:10.58052/IEEXG0317</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr"/>
@@ -19238,12 +19238,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031L</t>
+          <t>upland:10.58052/IEEXG031L</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
@@ -19286,12 +19286,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031Z</t>
+          <t>transition:10.58052/IEEXG031Z</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
@@ -19334,12 +19334,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032D</t>
+          <t>wetland:10.58052/IEEXG032D</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
@@ -19382,12 +19382,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032R</t>
+          <t>upland:10.58052/IEEXG032R</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
@@ -19430,12 +19430,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0335</t>
+          <t>transition:10.58052/IEEXG0335</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033J</t>
+          <t>wetland:10.58052/IEEXG033J</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
@@ -19526,12 +19526,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0353</t>
+          <t>upland:10.58052/IEEXG0353</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -19574,12 +19574,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035H</t>
+          <t>transition:10.58052/IEEXG035H</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
@@ -19622,12 +19622,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035V</t>
+          <t>wetland:10.58052/IEEXG035V</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
@@ -19670,12 +19670,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020A</t>
+          <t>upland:10.58052/IEEXG020A</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
@@ -19718,12 +19718,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020O</t>
+          <t>transition:10.58052/IEEXG020O</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
@@ -19766,12 +19766,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0212</t>
+          <t>wetland:10.58052/IEEXG0212</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
@@ -19814,12 +19814,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021G</t>
+          <t>upland:10.58052/IEEXG021G</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
@@ -19862,12 +19862,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021U</t>
+          <t>transition:10.58052/IEEXG021U</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
@@ -19910,12 +19910,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0228</t>
+          <t>wetland:10.58052/IEEXG0228</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
@@ -19958,12 +19958,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022M</t>
+          <t>upland:10.58052/IEEXG022M</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr"/>
@@ -20006,12 +20006,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0230</t>
+          <t>transition:10.58052/IEEXG0230</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
@@ -20054,12 +20054,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023E</t>
+          <t>wetland:10.58052/IEEXG023E</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr"/>
@@ -20102,12 +20102,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023S</t>
+          <t>upland:10.58052/IEEXG023S</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
@@ -20150,12 +20150,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0246</t>
+          <t>transition:10.58052/IEEXG0246</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr"/>
@@ -20198,12 +20198,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024K</t>
+          <t>wetland:10.58052/IEEXG024K</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr"/>
@@ -20246,12 +20246,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024Y</t>
+          <t>upland:10.58052/IEEXG024Y</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
@@ -20294,12 +20294,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025C</t>
+          <t>transition:10.58052/IEEXG025C</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
@@ -20342,12 +20342,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025Q</t>
+          <t>wetland:10.58052/IEEXG025Q</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
@@ -20390,12 +20390,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0264</t>
+          <t>upland:10.58052/IEEXG0264</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr"/>
@@ -20438,12 +20438,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026I</t>
+          <t>transition:10.58052/IEEXG026I</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
@@ -20486,12 +20486,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026W</t>
+          <t>wetland:10.58052/IEEXG026W</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr"/>
@@ -20534,12 +20534,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027A</t>
+          <t>upland:10.58052/IEEXG027A</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr"/>
@@ -20582,12 +20582,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027O</t>
+          <t>transition:10.58052/IEEXG027O</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr"/>
@@ -20630,12 +20630,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0282</t>
+          <t>wetland:10.58052/IEEXG0282</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr"/>
@@ -20678,12 +20678,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028G</t>
+          <t>upland:10.58052/IEEXG028G</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr"/>
@@ -20726,12 +20726,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028U</t>
+          <t>transition:10.58052/IEEXG028U</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr"/>
@@ -20774,12 +20774,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0298</t>
+          <t>wetland:10.58052/IEEXG0298</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
@@ -20822,12 +20822,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029M</t>
+          <t>upland:10.58052/IEEXG029M</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr"/>
@@ -20870,12 +20870,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02A0</t>
+          <t>transition:10.58052/IEEXG02A0</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr"/>
@@ -20918,12 +20918,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AE</t>
+          <t>wetland:10.58052/IEEXG02AE</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr"/>
@@ -20966,12 +20966,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AS</t>
+          <t>upland:10.58052/IEEXG02AS</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr"/>
@@ -21014,12 +21014,12 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B6</t>
+          <t>transition:10.58052/IEEXG02B6</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr"/>
@@ -21062,12 +21062,12 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BK</t>
+          <t>wetland:10.58052/IEEXG02BK</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
@@ -21110,12 +21110,12 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BY</t>
+          <t>upland:10.58052/IEEXG02BY</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
@@ -21158,12 +21158,12 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CC</t>
+          <t>transition:10.58052/IEEXG02CC</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr"/>
@@ -21206,12 +21206,12 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CQ</t>
+          <t>wetland:10.58052/IEEXG02CQ</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
@@ -21254,12 +21254,12 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D4</t>
+          <t>upland:10.58052/IEEXG02D4</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr"/>
@@ -21302,12 +21302,12 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DI</t>
+          <t>transition:10.58052/IEEXG02DI</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr"/>
@@ -21350,12 +21350,12 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DW</t>
+          <t>wetland:10.58052/IEEXG02DW</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr"/>
@@ -21398,12 +21398,12 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EA</t>
+          <t>upland:10.58052/IEEXG02EA</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr"/>
@@ -21446,12 +21446,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EO</t>
+          <t>transition:10.58052/IEEXG02EO</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr"/>
@@ -21494,12 +21494,12 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F2</t>
+          <t>wetland:10.58052/IEEXG02F2</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr"/>
@@ -21542,12 +21542,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FG</t>
+          <t>upland:10.58052/IEEXG02FG</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr"/>
@@ -21590,12 +21590,12 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FU</t>
+          <t>transition:10.58052/IEEXG02FU</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr"/>
@@ -21638,12 +21638,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G8</t>
+          <t>wetland:10.58052/IEEXG02G8</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr"/>
@@ -21686,12 +21686,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GM</t>
+          <t>upland:10.58052/IEEXG02GM</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
@@ -21734,12 +21734,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02H0</t>
+          <t>transition:10.58052/IEEXG02H0</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr"/>
@@ -21782,12 +21782,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HE</t>
+          <t>wetland:10.58052/IEEXG02HE</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr"/>
@@ -21830,12 +21830,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HS</t>
+          <t>upland:10.58052/IEEXG02HS</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr"/>
@@ -21878,12 +21878,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I6</t>
+          <t>transition:10.58052/IEEXG02I6</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr"/>
@@ -21926,12 +21926,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IK</t>
+          <t>wetland:10.58052/IEEXG02IK</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr"/>
@@ -21974,12 +21974,12 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IY</t>
+          <t>upland:10.58052/IEEXG02IY</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr"/>
@@ -22022,12 +22022,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JC</t>
+          <t>transition:10.58052/IEEXG02JC</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr"/>
@@ -22070,12 +22070,12 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JQ</t>
+          <t>wetland:10.58052/IEEXG02JQ</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr"/>
@@ -22118,12 +22118,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K4</t>
+          <t>upland:10.58052/IEEXG02K4</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
@@ -22166,12 +22166,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KI</t>
+          <t>transition:10.58052/IEEXG02KI</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr"/>
@@ -22214,12 +22214,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KW</t>
+          <t>wetland:10.58052/IEEXG02KW</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr"/>
@@ -22262,12 +22262,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LA</t>
+          <t>upland:10.58052/IEEXG02LA</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr"/>
@@ -22310,12 +22310,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LO</t>
+          <t>transition:10.58052/IEEXG02LO</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr"/>
@@ -22358,12 +22358,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M2</t>
+          <t>wetland:10.58052/IEEXG02M2</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
@@ -22406,12 +22406,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MG</t>
+          <t>upland:10.58052/IEEXG02MG</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr"/>
@@ -22454,12 +22454,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MU</t>
+          <t>transition:10.58052/IEEXG02MU</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr"/>
@@ -22502,12 +22502,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N8</t>
+          <t>wetland:10.58052/IEEXG02N8</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr"/>
@@ -22550,12 +22550,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NM</t>
+          <t>upland:10.58052/IEEXG02NM</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr"/>
@@ -22598,12 +22598,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02O0</t>
+          <t>transition:10.58052/IEEXG02O0</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr"/>
@@ -22646,12 +22646,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OE</t>
+          <t>wetland:10.58052/IEEXG02OE</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr"/>
@@ -22694,12 +22694,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OS</t>
+          <t>upland:10.58052/IEEXG02OS</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr"/>
@@ -22742,12 +22742,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P6</t>
+          <t>transition:10.58052/IEEXG02P6</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr"/>
@@ -22790,12 +22790,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PK</t>
+          <t>wetland:10.58052/IEEXG02PK</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr"/>
@@ -22838,12 +22838,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PY</t>
+          <t>upland:10.58052/IEEXG02PY</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr"/>
@@ -22886,12 +22886,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QC</t>
+          <t>transition:10.58052/IEEXG02QC</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr"/>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QQ</t>
+          <t>wetland:10.58052/IEEXG02QQ</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr"/>
@@ -22982,12 +22982,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SA</t>
+          <t>upland:10.58052/IEEXG02SA</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr"/>
@@ -23030,12 +23030,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SO</t>
+          <t>transition:10.58052/IEEXG02SO</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr"/>
@@ -23078,12 +23078,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T2</t>
+          <t>wetland:10.58052/IEEXG02T2</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr"/>
@@ -23126,12 +23126,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TG</t>
+          <t>upland:10.58052/IEEXG02TG</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr"/>
@@ -23174,12 +23174,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TU</t>
+          <t>transition:10.58052/IEEXG02TU</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr"/>
@@ -23222,12 +23222,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U8</t>
+          <t>wetland:10.58052/IEEXG02U8</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr"/>
@@ -23270,12 +23270,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UM</t>
+          <t>upland:10.58052/IEEXG02UM</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr"/>
@@ -23318,12 +23318,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02V0</t>
+          <t>transition:10.58052/IEEXG02V0</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr"/>
@@ -23366,12 +23366,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VE</t>
+          <t>wetland:10.58052/IEEXG02VE</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr"/>
@@ -23414,12 +23414,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VS</t>
+          <t>upland:10.58052/IEEXG02VS</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr"/>
@@ -23462,12 +23462,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W6</t>
+          <t>transition:10.58052/IEEXG02W6</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr"/>
@@ -23510,12 +23510,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WK</t>
+          <t>wetland:10.58052/IEEXG02WK</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr"/>
@@ -23558,12 +23558,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y4</t>
+          <t>upland:10.58052/IEEXG02Y4</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr"/>
@@ -23606,12 +23606,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YI</t>
+          <t>transition:10.58052/IEEXG02YI</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr"/>
@@ -23654,12 +23654,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YW</t>
+          <t>wetland:10.58052/IEEXG02YW</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr"/>
@@ -23702,12 +23702,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZA</t>
+          <t>upland:10.58052/IEEXG02ZA</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr"/>
@@ -23750,12 +23750,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZO</t>
+          <t>transition:10.58052/IEEXG02ZO</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr"/>
@@ -23798,12 +23798,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0302</t>
+          <t>wetland:10.58052/IEEXG0302</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr"/>
@@ -23846,12 +23846,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030G</t>
+          <t>upland:10.58052/IEEXG030G</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr"/>
@@ -23894,12 +23894,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030U</t>
+          <t>transition:10.58052/IEEXG030U</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr"/>
@@ -23942,12 +23942,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0318</t>
+          <t>wetland:10.58052/IEEXG0318</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr"/>
@@ -23990,12 +23990,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031M</t>
+          <t>upland:10.58052/IEEXG031M</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr"/>
@@ -24038,12 +24038,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0320</t>
+          <t>transition:10.58052/IEEXG0320</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr"/>
@@ -24086,12 +24086,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032E</t>
+          <t>wetland:10.58052/IEEXG032E</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr"/>
@@ -24134,12 +24134,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032S</t>
+          <t>upland:10.58052/IEEXG032S</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr"/>
@@ -24182,12 +24182,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0336</t>
+          <t>transition:10.58052/IEEXG0336</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr"/>
@@ -24230,12 +24230,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033K</t>
+          <t>wetland:10.58052/IEEXG033K</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr"/>
@@ -24278,12 +24278,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0354</t>
+          <t>upland:10.58052/IEEXG0354</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr"/>
@@ -24326,12 +24326,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035I</t>
+          <t>transition:10.58052/IEEXG035I</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr"/>
@@ -24374,12 +24374,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035W</t>
+          <t>wetland:10.58052/IEEXG035W</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr"/>
